--- a/artfynd/A 28888-2026 artfynd.xlsx
+++ b/artfynd/A 28888-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135646887</v>
       </c>
       <c r="B2" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646872</v>
       </c>
       <c r="B3" t="n">
-        <v>99240</v>
+        <v>99267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>135646874</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135646882</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135646875</v>
       </c>
       <c r="B6" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>135646880</v>
       </c>
       <c r="B7" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135646883</v>
       </c>
       <c r="B8" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>135646876</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135646890</v>
       </c>
       <c r="B10" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,32 +1714,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135646866</v>
+        <v>135646893</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1749,13 +1749,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568746</v>
+        <v>568525</v>
       </c>
       <c r="R11" t="n">
-        <v>7003609</v>
+        <v>7003488</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,38 +1820,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135646866</t>
+          <t>https://artportalen.se/Sighting/135646893</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135646867</v>
+        <v>135646877</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>99269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568754</v>
+        <v>568512</v>
       </c>
       <c r="R12" t="n">
-        <v>7003593</v>
+        <v>7003366</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,38 +1932,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135646867</t>
+          <t>https://artportalen.se/Sighting/135646877</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135646868</v>
+        <v>135646878</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>99269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568762</v>
+        <v>568498</v>
       </c>
       <c r="R13" t="n">
-        <v>7003572</v>
+        <v>7003359</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,38 +2044,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135646868</t>
+          <t>https://artportalen.se/Sighting/135646878</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135646893</v>
+        <v>135646879</v>
       </c>
       <c r="B14" t="n">
-        <v>99266</v>
+        <v>99269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568525</v>
+        <v>568431</v>
       </c>
       <c r="R14" t="n">
-        <v>7003488</v>
+        <v>7003311</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,16 +2156,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135646893</t>
+          <t>https://artportalen.se/Sighting/135646879</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135646877</v>
+        <v>135646888</v>
       </c>
       <c r="B15" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568512</v>
+        <v>568393</v>
       </c>
       <c r="R15" t="n">
-        <v>7003366</v>
+        <v>7003360</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,16 +2268,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135646877</t>
+          <t>https://artportalen.se/Sighting/135646888</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135646878</v>
+        <v>135646889</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568498</v>
+        <v>568397</v>
       </c>
       <c r="R16" t="n">
-        <v>7003359</v>
+        <v>7003368</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,16 +2380,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135646878</t>
+          <t>https://artportalen.se/Sighting/135646889</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135646879</v>
+        <v>135646891</v>
       </c>
       <c r="B17" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568431</v>
+        <v>568456</v>
       </c>
       <c r="R17" t="n">
-        <v>7003311</v>
+        <v>7003382</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,342 +2491,6 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135646879</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>135646888</v>
-      </c>
-      <c r="B18" t="n">
-        <v>99242</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Hambergsmyran, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>568393</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7003360</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135646888</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>135646889</v>
-      </c>
-      <c r="B19" t="n">
-        <v>99242</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Hambergsmyran, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>568397</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7003368</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135646889</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>135646891</v>
-      </c>
-      <c r="B20" t="n">
-        <v>99242</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Hambergsmyran, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>568456</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7003382</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135646891</t>
         </is>
@@ -2850,9 +2514,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28888-2026 artfynd.xlsx
+++ b/artfynd/A 28888-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646887</v>
       </c>
       <c r="B2" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646872</v>
       </c>
       <c r="B3" t="n">
-        <v>99272</v>
+        <v>99274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>135646874</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135646882</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135646875</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>135646880</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135646883</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135646893</v>
       </c>
       <c r="B11" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135646877</v>
       </c>
       <c r="B12" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135646878</v>
       </c>
       <c r="B13" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>135646879</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135646888</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>135646889</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135646891</v>
       </c>
       <c r="B17" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28888-2026 artfynd.xlsx
+++ b/artfynd/A 28888-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646887</v>
       </c>
       <c r="B2" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646872</v>
       </c>
       <c r="B3" t="n">
-        <v>99274</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>135646874</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135646882</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135646875</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>135646880</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135646883</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>135646876</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135646890</v>
       </c>
       <c r="B10" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135646893</v>
       </c>
       <c r="B11" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135646877</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135646878</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>135646879</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135646888</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>135646889</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135646891</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28888-2026 artfynd.xlsx
+++ b/artfynd/A 28888-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646887</v>
       </c>
       <c r="B2" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646872</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>135646874</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135646882</v>
       </c>
       <c r="B5" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135646875</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>135646880</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135646883</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>135646876</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135646890</v>
       </c>
       <c r="B10" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135646893</v>
       </c>
       <c r="B11" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135646877</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135646878</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>135646879</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135646888</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>135646889</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135646891</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28888-2026 artfynd.xlsx
+++ b/artfynd/A 28888-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646887</v>
       </c>
       <c r="B2" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646872</v>
       </c>
       <c r="B3" t="n">
-        <v>99292</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>135646874</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135646882</v>
       </c>
       <c r="B5" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135646875</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>135646880</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135646883</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135646893</v>
       </c>
       <c r="B11" t="n">
-        <v>99318</v>
+        <v>99319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135646877</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135646878</v>
       </c>
       <c r="B13" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>135646879</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135646888</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>135646889</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135646891</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28888-2026 artfynd.xlsx
+++ b/artfynd/A 28888-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646887</v>
       </c>
       <c r="B2" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646872</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>135646874</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135646882</v>
       </c>
       <c r="B5" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135646875</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>135646880</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135646883</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>135646876</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135646890</v>
       </c>
       <c r="B10" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135646893</v>
       </c>
       <c r="B11" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135646877</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135646878</v>
       </c>
       <c r="B13" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>135646879</v>
       </c>
       <c r="B14" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135646888</v>
       </c>
       <c r="B15" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>135646889</v>
       </c>
       <c r="B16" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135646891</v>
       </c>
       <c r="B17" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28888-2026 artfynd.xlsx
+++ b/artfynd/A 28888-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646887</v>
       </c>
       <c r="B2" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646872</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>135646874</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135646882</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135646875</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>135646880</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>135646883</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>135646876</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135646890</v>
       </c>
       <c r="B10" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>135646893</v>
       </c>
       <c r="B11" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135646877</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135646878</v>
       </c>
       <c r="B13" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>135646879</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135646888</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>135646889</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>135646891</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
